--- a/data/trans_camb/IP2001-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Edad-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,44</t>
+          <t>0,0; 11,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 5,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 8,09</t>
+          <t>0,3; 7,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 7,88</t>
+          <t>0,47; 8,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,2</t>
+          <t>-3,76; 2,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,58</t>
+          <t>-1,25; 5,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 5,93</t>
+          <t>-0,49; 6,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,65</t>
+          <t>-2,48; 4,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,43</t>
+          <t>0,38; 5,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,95</t>
+          <t>0,64; 5,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,34</t>
+          <t>-2,29; 2,4</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 253,81</t>
+          <t>3,23; 253,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 262,96</t>
+          <t>0,43; 243,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,17; 70,88</t>
+          <t>-67,87; 73,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 188,68</t>
+          <t>-25,48; 172,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 196,99</t>
+          <t>-10,97; 203,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 143,94</t>
+          <t>-46,83; 140,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 161,66</t>
+          <t>6,95; 158,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,92; 169,3</t>
+          <t>9,23; 162,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,29; 69,78</t>
+          <t>-41,33; 69,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 7,89</t>
+          <t>-5,99; 8,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 8,15</t>
+          <t>-4,29; 8,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,46; -2,27</t>
+          <t>-13,64; -2,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 6,03</t>
+          <t>-6,94; 6,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 10,04</t>
+          <t>-3,48; 9,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -1,63</t>
+          <t>-13,25; -1,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 5,3</t>
+          <t>-4,74; 4,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 6,86</t>
+          <t>-2,04; 7,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,28; -3,44</t>
+          <t>-11,1; -3,24</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 75,33</t>
+          <t>-35,57; 75,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 77,6</t>
+          <t>-25,7; 82,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,51; -15,13</t>
+          <t>-76,85; -14,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,55; 55,82</t>
+          <t>-40,98; 61,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 99,18</t>
+          <t>-20,64; 93,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,81; -13,16</t>
+          <t>-75,1; -10,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 50,37</t>
+          <t>-28,01; 40,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 62,33</t>
+          <t>-12,7; 68,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,29; -27,95</t>
+          <t>-70,34; -28,37</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 3,14</t>
+          <t>-8,03; 3,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 4,74</t>
+          <t>-6,36; 5,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,03; -5,17</t>
+          <t>-14,08; -5,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 10,36</t>
+          <t>-1,48; 9,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 3,67</t>
+          <t>-7,0; 3,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 0,18</t>
+          <t>-9,71; -0,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 4,94</t>
+          <t>-3,19; 4,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 3,06</t>
+          <t>-5,32; 2,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -3,64</t>
+          <t>-10,35; -3,91</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,72; 30,44</t>
+          <t>-51,43; 33,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,16; 43,91</t>
+          <t>-40,8; 51,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-85,64; -48,75</t>
+          <t>-85,35; -47,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 114,23</t>
+          <t>-9,78; 111,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,58; 42,64</t>
+          <t>-50,01; 40,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,0; 4,09</t>
+          <t>-66,63; -1,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 49,33</t>
+          <t>-22,57; 44,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 29,72</t>
+          <t>-36,53; 22,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,17; -34,51</t>
+          <t>-70,34; -35,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,33</t>
+          <t>-1,45; 3,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 4,59</t>
+          <t>-0,72; 4,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -1,95</t>
+          <t>-6,17; -1,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,8</t>
+          <t>-1,31; 3,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,16</t>
+          <t>-0,65; 4,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,43</t>
+          <t>-4,45; 0,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,0</t>
+          <t>-0,66; 3,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,81</t>
+          <t>0,03; 3,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -1,25</t>
+          <t>-4,53; -1,35</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 45,07</t>
+          <t>-15,29; 50,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 62,88</t>
+          <t>-8,4; 61,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-64,77; -25,68</t>
+          <t>-64,09; -21,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 54,55</t>
+          <t>-14,33; 55,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 60,9</t>
+          <t>-7,84; 65,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 7,15</t>
+          <t>-46,15; 5,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 40,73</t>
+          <t>-6,94; 40,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,32; 51,64</t>
+          <t>-0,07; 49,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-49,76; -15,91</t>
+          <t>-50,1; -17,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2001-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Edad-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,52</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,54</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,88</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 7,79</t>
+          <t>0,47; 7,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 8,01</t>
+          <t>0,16; 8,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 2,15</t>
+          <t>-4,27; 2,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,42</t>
+          <t>-1,09; 5,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,17</t>
+          <t>-0,85; 5,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 4,58</t>
+          <t>-2,33; 4,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,36</t>
+          <t>0,66; 5,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,86</t>
+          <t>0,92; 5,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,4</t>
+          <t>-2,12; 2,72</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 253,0</t>
+          <t>5,41; 250,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 243,24</t>
+          <t>1,05; 242,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,87; 73,59</t>
+          <t>-71,74; 67,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 172,82</t>
+          <t>-20,55; 185,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 203,46</t>
+          <t>-18,88; 173,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 140,31</t>
+          <t>-42,42; 152,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 158,87</t>
+          <t>11,11; 155,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 162,66</t>
+          <t>15,09; 168,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-41,33; 69,09</t>
+          <t>-40,94; 74,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 8,12</t>
+          <t>-5,82; 7,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 8,48</t>
+          <t>-4,17; 8,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,64; -2,01</t>
+          <t>-14,01; -2,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 6,22</t>
+          <t>-7,02; 5,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 9,32</t>
+          <t>-3,09; 9,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -1,46</t>
+          <t>-12,72; -1,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 4,77</t>
+          <t>-4,57; 4,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 7,4</t>
+          <t>-2,23; 6,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -3,24</t>
+          <t>-11,76; -3,41</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,57; 75,44</t>
+          <t>-32,87; 76,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,7; 82,37</t>
+          <t>-25,15; 88,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,85; -14,29</t>
+          <t>-75,9; -17,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 61,55</t>
+          <t>-41,88; 51,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 93,44</t>
+          <t>-19,06; 94,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,1; -10,22</t>
+          <t>-73,96; -12,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 40,97</t>
+          <t>-27,5; 42,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 68,0</t>
+          <t>-13,82; 61,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,34; -28,37</t>
+          <t>-70,47; -28,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 3,43</t>
+          <t>-8,34; 2,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 5,4</t>
+          <t>-6,32; 4,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,08; -5,17</t>
+          <t>-13,81; -5,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 9,97</t>
+          <t>-1,71; 8,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 3,62</t>
+          <t>-7,09; 3,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,71; -0,18</t>
+          <t>-9,32; -0,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,67</t>
+          <t>-3,25; 4,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 2,28</t>
+          <t>-5,35; 2,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,35; -3,91</t>
+          <t>-9,99; -3,76</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,43; 33,25</t>
+          <t>-51,63; 27,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,8; 51,52</t>
+          <t>-41,13; 46,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-85,35; -47,88</t>
+          <t>-85,39; -48,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 111,8</t>
+          <t>-13,33; 85,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,01; 40,16</t>
+          <t>-48,67; 38,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,63; -1,37</t>
+          <t>-64,79; -0,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 44,74</t>
+          <t>-23,1; 46,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 22,72</t>
+          <t>-37,45; 27,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,34; -35,41</t>
+          <t>-70,92; -35,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,56</t>
+          <t>-1,73; 3,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,6</t>
+          <t>-0,39; 4,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,17; -1,59</t>
+          <t>-6,37; -2,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,78</t>
+          <t>-1,09; 4,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,34</t>
+          <t>-0,72; 4,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,32</t>
+          <t>-4,51; 0,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,03</t>
+          <t>-0,64; 2,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,66</t>
+          <t>-0,04; 3,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -1,35</t>
+          <t>-4,55; -1,36</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 50,27</t>
+          <t>-18,44; 51,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 61,07</t>
+          <t>-5,29; 65,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-64,09; -21,4</t>
+          <t>-65,93; -27,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 55,0</t>
+          <t>-12,13; 58,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 65,34</t>
+          <t>-8,44; 58,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,15; 5,79</t>
+          <t>-48,1; 5,51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 40,94</t>
+          <t>-7,07; 39,14</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 49,71</t>
+          <t>-0,43; 47,95</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,1; -17,91</t>
+          <t>-50,99; -18,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2001-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -629,14 +629,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -644,19 +644,19 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>3,32</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,33</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>1,76</t>
         </is>
       </c>
     </row>
@@ -682,14 +682,14 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,58</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,31</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -697,27 +697,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 11,45</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,04</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,97</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,07</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,0</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 7,75</t>
+          <t>-1,25; 5,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 8,11</t>
+          <t>-0,96; 5,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 2,02</t>
+          <t>-2,2; 5,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 5,47</t>
+          <t>0,46; 8,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 5,76</t>
+          <t>0,6; 7,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 4,74</t>
+          <t>-4,14; 2,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,32</t>
+          <t>0,51; 5,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,95</t>
+          <t>0,79; 5,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,72</t>
+          <t>-2,08; 2,61</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>58,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26,12%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>88,28%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>90,53%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-22,25%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46,04%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>58,78%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>-21,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-0,09%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 250,72</t>
+          <t>-23,91; 188,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 242,46</t>
+          <t>-18,37; 196,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,74; 67,88</t>
+          <t>-41,5; 159,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 185,43</t>
+          <t>1,51; 253,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 173,47</t>
+          <t>3,78; 262,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 152,72</t>
+          <t>-71,65; 73,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,11; 155,21</t>
+          <t>8,8; 161,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,09; 168,03</t>
+          <t>11,92; 169,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,94; 74,57</t>
+          <t>-40,72; 72,62</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,38</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-6,76</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,96</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-7,64</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,04</t>
+          <t>-7,6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,32</t>
+          <t>-7,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 7,74</t>
+          <t>-7,06; 6,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 8,83</t>
+          <t>-3,13; 10,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,01; -2,04</t>
+          <t>-12,64; -1,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 5,41</t>
+          <t>-4,92; 7,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 9,76</t>
+          <t>-4,44; 8,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -1,66</t>
+          <t>-13,43; -2,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 4,78</t>
+          <t>-4,61; 5,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 6,99</t>
+          <t>-2,62; 6,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,76; -3,41</t>
+          <t>-11,09; -3,12</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-3,69%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24,82%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-49,72%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>8,13%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>14,1%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-55,04%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-3,69%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-51,78%</t>
+          <t>-54,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-53,29%</t>
+          <t>-52,09%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 76,77</t>
+          <t>-41,55; 55,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 88,96</t>
+          <t>-19,13; 99,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,9; -17,13</t>
+          <t>-74,11; -10,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 51,32</t>
+          <t>-30,16; 75,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 94,98</t>
+          <t>-26,12; 77,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,96; -12,06</t>
+          <t>-77,8; -14,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 42,24</t>
+          <t>-27,57; 50,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 61,11</t>
+          <t>-15,03; 62,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,47; -28,24</t>
+          <t>-68,34; -25,68</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,89</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,98</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,72</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,27</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,75</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,89</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,89</t>
+          <t>-8,81</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,99</t>
+          <t>-6,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 2,78</t>
+          <t>-1,9; 10,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,86</t>
+          <t>-6,7; 3,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,81; -5,14</t>
+          <t>-9,8; -0,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 8,51</t>
+          <t>-7,3; 3,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 3,44</t>
+          <t>-6,62; 4,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,32; -0,25</t>
+          <t>-13,45; -4,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 4,89</t>
+          <t>-3,1; 4,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 2,86</t>
+          <t>-5,22; 3,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -3,76</t>
+          <t>-10,03; -3,53</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>31,62%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-15,89%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-41,97%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-17,99%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-5,54%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-70,87%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>31,62%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-15,89%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-41,23%</t>
+          <t>-67,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-56,1%</t>
+          <t>-54,54%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,63; 27,32</t>
+          <t>-12,78; 114,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 46,73</t>
+          <t>-47,58; 42,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-85,39; -48,52</t>
+          <t>-66,57; 2,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 85,5</t>
+          <t>-48,72; 30,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,67; 38,73</t>
+          <t>-43,16; 43,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,79; -0,77</t>
+          <t>-81,91; -43,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 46,97</t>
+          <t>-22,25; 49,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,45; 27,45</t>
+          <t>-36,91; 29,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,92; -35,29</t>
+          <t>-69,62; -33,0</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,43</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,73</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,8</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,06</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,09</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,98</t>
+          <t>-3,84</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,98</t>
+          <t>-2,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,68</t>
+          <t>-1,1; 3,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,77</t>
+          <t>-0,7; 4,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -2,0</t>
+          <t>-3,92; 0,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,02</t>
+          <t>-1,54; 3,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,18</t>
+          <t>-0,77; 4,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,36</t>
+          <t>-5,93; -1,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,88</t>
+          <t>-0,66; 3,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 3,51</t>
+          <t>0,03; 3,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -1,36</t>
+          <t>-4,38; -0,99</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>17,89%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-22,58%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>24,4%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-48,49%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-24,84%</t>
+          <t>-45,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-36,29%</t>
+          <t>-33,78%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 51,43</t>
+          <t>-12,22; 54,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 65,8</t>
+          <t>-8,08; 60,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,93; -27,1</t>
+          <t>-44,79; 9,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 58,14</t>
+          <t>-16,21; 45,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 58,86</t>
+          <t>-7,86; 62,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 5,51</t>
+          <t>-62,86; -22,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 39,14</t>
+          <t>-7,15; 40,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 47,95</t>
+          <t>1,32; 51,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,99; -18,58</t>
+          <t>-47,96; -13,35</t>
         </is>
       </c>
     </row>
